--- a/Online Form BUT-JP.xlsx
+++ b/Online Form BUT-JP.xlsx
@@ -5,6 +5,7 @@
   <sheets>
     <sheet state="visible" name="Profiles" sheetId="1" r:id="rId5"/>
     <sheet state="visible" name="Survey" sheetId="2" r:id="rId6"/>
+    <sheet state="visible" name="HVAC" sheetId="3" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -12,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="98">
   <si>
     <t>participant_id</t>
   </si>
@@ -41,10 +42,10 @@
     <t>created_at</t>
   </si>
   <si>
-    <t>PA6VQZ</t>
-  </si>
-  <si>
-    <t>123@vutbr.cz</t>
+    <t>PF3LSE</t>
+  </si>
+  <si>
+    <t>xmpokor25@vutbr.cz</t>
   </si>
   <si>
     <t>male</t>
@@ -53,7 +54,43 @@
     <t>Czech</t>
   </si>
   <si>
-    <t>2026-04-24T07:03:43.230Z</t>
+    <t>2026-06-08T07:21:30.213Z</t>
+  </si>
+  <si>
+    <t>PZJJPG</t>
+  </si>
+  <si>
+    <t>janfv.pokorny@gmail.com</t>
+  </si>
+  <si>
+    <t>USA</t>
+  </si>
+  <si>
+    <t>2026-06-08T07:40:43.144Z</t>
+  </si>
+  <si>
+    <t>PKH8Z6</t>
+  </si>
+  <si>
+    <t>xmpokor24@vutbr.cz</t>
+  </si>
+  <si>
+    <t>UK</t>
+  </si>
+  <si>
+    <t>2026-06-08T07:55:40.150Z</t>
+  </si>
+  <si>
+    <t>PUHNVV</t>
+  </si>
+  <si>
+    <t>xmpokor26@vutbr.cz</t>
+  </si>
+  <si>
+    <t>Australia</t>
+  </si>
+  <si>
+    <t>2026-06-08T08:05:04.469Z</t>
   </si>
   <si>
     <t>timestamp</t>
@@ -86,74 +123,197 @@
     <t>wanted_action</t>
   </si>
   <si>
-    <t>2026-04-24T06:56:10.014Z</t>
+    <t>2026-06-08T07:33:53.336Z</t>
+  </si>
+  <si>
+    <t>ABC</t>
+  </si>
+  <si>
+    <t>1_light_summer</t>
+  </si>
+  <si>
+    <t>driver</t>
+  </si>
+  <si>
+    <t>street</t>
+  </si>
+  <si>
+    <t>2026-06-08T07:33:48.607Z</t>
+  </si>
+  <si>
+    <t>Whole body (initial)</t>
+  </si>
+  <si>
+    <t>Upper back</t>
+  </si>
+  <si>
+    <t>Lower back</t>
+  </si>
+  <si>
+    <t>Seat</t>
+  </si>
+  <si>
+    <t>Thighs back</t>
+  </si>
+  <si>
+    <t>Face</t>
+  </si>
+  <si>
+    <t>Head</t>
+  </si>
+  <si>
+    <t>Chest</t>
+  </si>
+  <si>
+    <t>Arms</t>
+  </si>
+  <si>
+    <t>Hands</t>
+  </si>
+  <si>
+    <t>Thighs front</t>
+  </si>
+  <si>
+    <t>Calves + Shins</t>
+  </si>
+  <si>
+    <t>Feet</t>
+  </si>
+  <si>
+    <t>Whole body (overall)</t>
+  </si>
+  <si>
+    <t>2026-06-08T07:40:08.072Z</t>
+  </si>
+  <si>
+    <t>CDF</t>
+  </si>
+  <si>
+    <t>front_passenger</t>
+  </si>
+  <si>
+    <t>2026-06-08T07:34:15.458Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>2026-06-08T07:41:02.198Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T07:55:02.592Z</t>
+  </si>
+  <si>
+    <t>FGH</t>
+  </si>
+  <si>
+    <t>2026-06-08T07:46:25.320Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T08:05:23.347Z</t>
   </si>
   <si>
     <t>unknown</t>
   </si>
   <si>
-    <t>Whole body (initial)</t>
-  </si>
-  <si>
-    <t>Upper back</t>
-  </si>
-  <si>
-    <t>Lower back</t>
-  </si>
-  <si>
-    <t>Seat</t>
-  </si>
-  <si>
-    <t>Thighs back</t>
-  </si>
-  <si>
-    <t>Face</t>
-  </si>
-  <si>
-    <t>Head</t>
-  </si>
-  <si>
-    <t>Chest</t>
-  </si>
-  <si>
-    <t>Arms</t>
-  </si>
-  <si>
-    <t>Hands</t>
-  </si>
-  <si>
-    <t>Thighs front</t>
-  </si>
-  <si>
-    <t>Calves + Shins</t>
-  </si>
-  <si>
-    <t>Feet</t>
-  </si>
-  <si>
-    <t>Whole body (overall)</t>
-  </si>
-  <si>
-    <t>2026-04-24T06:57:24.702Z</t>
-  </si>
-  <si>
-    <t>2026-04-24T06:58:40.599Z</t>
-  </si>
-  <si>
-    <t>2026-04-24T06:59:01.440Z</t>
-  </si>
-  <si>
-    <t>2026-04-24T07:02:51.033Z</t>
-  </si>
-  <si>
-    <t>2026-04-24T07:03:54.209Z</t>
+    <t>2026-06-08T08:05:17.433Z</t>
+  </si>
+  <si>
+    <t>2026-06-08T08:05:36.179Z</t>
+  </si>
+  <si>
+    <t>TRT</t>
+  </si>
+  <si>
+    <t>hvac_vent_driver</t>
+  </si>
+  <si>
+    <t>hvac_vent_passenger</t>
+  </si>
+  <si>
+    <t>hvac_vent_rear_left</t>
+  </si>
+  <si>
+    <t>hvac_vent_rear_right</t>
+  </si>
+  <si>
+    <t>hvac_airflow_sources</t>
+  </si>
+  <si>
+    <t>hvac_fan_intensity</t>
+  </si>
+  <si>
+    <t>hvac_sw_heat_level</t>
+  </si>
+  <si>
+    <t>hvac_driver_seat_climate</t>
+  </si>
+  <si>
+    <t>hvac_codriver_seat_climate</t>
+  </si>
+  <si>
+    <t>hvac_ac_compressor</t>
+  </si>
+  <si>
+    <t>hvac_recirculation</t>
+  </si>
+  <si>
+    <t>hvac_auto_mode</t>
+  </si>
+  <si>
+    <t>hvac_temp_set</t>
+  </si>
+  <si>
+    <t>hvac_time_offset_sec</t>
+  </si>
+  <si>
+    <t>time_gap_warning</t>
+  </si>
+  <si>
+    <t>2026-06-08T08:05:51.685Z</t>
+  </si>
+  <si>
+    <t>off</t>
+  </si>
+  <si>
+    <t>heat2</t>
+  </si>
+  <si>
+    <t>heat1</t>
+  </si>
+  <si>
+    <t>auto</t>
+  </si>
+  <si>
+    <t>manual</t>
+  </si>
+  <si>
+    <t>2026-06-08T08:06:47.283Z</t>
+  </si>
+  <si>
+    <t>dashboard|feet|torso|windshield_defroster|rear_defroster</t>
+  </si>
+  <si>
+    <t>on</t>
+  </si>
+  <si>
+    <t>heat3</t>
+  </si>
+  <si>
+    <t>2026-06-08T08:28:53.265Z</t>
+  </si>
+  <si>
+    <t>cool3</t>
+  </si>
+  <si>
+    <t>cool1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -164,6 +324,11 @@
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -180,7 +345,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -189,6 +354,9 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -203,6 +371,10 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -448,16 +620,16 @@
         <v>10</v>
       </c>
       <c r="C2" s="1">
-        <v>28.0</v>
+        <v>42.0</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E2" s="1">
-        <v>172.0</v>
+        <v>180.0</v>
       </c>
       <c r="F2" s="1">
-        <v>70.0</v>
+        <v>97.0</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>12</v>
@@ -467,6 +639,93 @@
       </c>
       <c r="I2" s="1" t="s">
         <v>13</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="1">
+        <v>28.0</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="1">
+        <v>172.0</v>
+      </c>
+      <c r="F3" s="1">
+        <v>70.0</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="1">
+        <v>23.0</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="1">
+        <v>121.0</v>
+      </c>
+      <c r="F4" s="1">
+        <v>72.0</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="1">
+        <v>102.0</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="1">
+        <v>102.0</v>
+      </c>
+      <c r="F5" s="1">
+        <v>102.0</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H5" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -483,54 +742,66 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>25</v>
+        <v>37</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="I2" s="2">
         <v>0.0</v>
       </c>
       <c r="J2" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="K2" s="2">
         <v>0.0</v>
@@ -538,13 +809,25 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>25</v>
+        <v>37</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="I3" s="2">
         <v>0.0</v>
@@ -558,13 +841,25 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>25</v>
+        <v>37</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="I4" s="2">
         <v>0.0</v>
@@ -578,13 +873,25 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>25</v>
+        <v>37</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="I5" s="2">
         <v>0.0</v>
@@ -598,13 +905,25 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>25</v>
+        <v>37</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="I6" s="2">
         <v>0.0</v>
@@ -618,13 +937,25 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>25</v>
+        <v>37</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="I7" s="2">
         <v>0.0</v>
@@ -638,13 +969,25 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>25</v>
+        <v>37</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="I8" s="2">
         <v>0.0</v>
@@ -658,13 +1001,25 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>25</v>
+        <v>37</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="I9" s="2">
         <v>0.0</v>
@@ -678,13 +1033,25 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>25</v>
+        <v>37</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="I10" s="2">
         <v>0.0</v>
@@ -698,13 +1065,25 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>25</v>
+        <v>37</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="I11" s="2">
         <v>0.0</v>
@@ -718,13 +1097,25 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>25</v>
+        <v>37</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="I12" s="2">
         <v>0.0</v>
@@ -738,13 +1129,25 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>25</v>
+        <v>37</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="I13" s="2">
         <v>0.0</v>
@@ -758,13 +1161,25 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>25</v>
+        <v>37</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="I14" s="2">
         <v>0.0</v>
@@ -778,13 +1193,25 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>25</v>
+        <v>37</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="I15" s="2">
         <v>0.0</v>
@@ -798,19 +1225,25 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>25</v>
+        <v>57</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="I16" s="2">
         <v>0.0</v>
       </c>
       <c r="J16" s="2">
-        <v>0.0</v>
+        <v>1.5</v>
       </c>
       <c r="K16" s="2">
         <v>0.0</v>
@@ -818,13 +1251,19 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>25</v>
+        <v>57</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="I17" s="2">
         <v>0.0</v>
@@ -838,13 +1277,19 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>25</v>
+        <v>57</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="I18" s="2">
         <v>0.0</v>
@@ -854,17 +1299,26 @@
       </c>
       <c r="K18" s="2">
         <v>0.0</v>
+      </c>
+      <c r="T18" s="1" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>25</v>
+        <v>57</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="I19" s="2">
         <v>0.0</v>
@@ -873,18 +1327,24 @@
         <v>2.0</v>
       </c>
       <c r="K19" s="2">
-        <v>0.0</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>25</v>
+        <v>57</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="I20" s="2">
         <v>0.0</v>
@@ -898,13 +1358,19 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>25</v>
+        <v>57</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="I21" s="2">
         <v>0.0</v>
@@ -918,13 +1384,19 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>25</v>
+        <v>57</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="I22" s="2">
         <v>0.0</v>
@@ -938,13 +1410,19 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>25</v>
+        <v>57</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="I23" s="2">
         <v>0.0</v>
@@ -958,13 +1436,19 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>25</v>
+        <v>57</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="I24" s="2">
         <v>0.0</v>
@@ -978,13 +1462,19 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>25</v>
+        <v>57</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="I25" s="2">
         <v>0.0</v>
@@ -998,13 +1488,19 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>25</v>
+        <v>57</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="I26" s="2">
         <v>0.0</v>
@@ -1018,13 +1514,19 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>25</v>
+        <v>57</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="I27" s="2">
         <v>0.0</v>
@@ -1038,13 +1540,19 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>25</v>
+        <v>57</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="I28" s="2">
         <v>0.0</v>
@@ -1058,13 +1566,19 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>25</v>
+        <v>57</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="I29" s="2">
         <v>0.0</v>
@@ -1078,13 +1592,19 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>25</v>
+        <v>14</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="I30" s="2">
         <v>0.0</v>
@@ -1098,39 +1618,51 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>25</v>
+        <v>14</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="I31" s="2">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="J31" s="2">
-        <v>2.0</v>
+        <v>-1.5</v>
       </c>
       <c r="K31" s="2">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>25</v>
+        <v>14</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="I32" s="2">
-        <v>0.0</v>
+        <v>-2.5</v>
       </c>
       <c r="J32" s="2">
-        <v>2.0</v>
+        <v>-0.5</v>
       </c>
       <c r="K32" s="2">
         <v>0.0</v>
@@ -1138,13 +1670,19 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>25</v>
+        <v>14</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="I33" s="2">
         <v>0.0</v>
@@ -1158,13 +1696,19 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>25</v>
+        <v>14</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="I34" s="2">
         <v>0.0</v>
@@ -1178,13 +1722,19 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>25</v>
+        <v>14</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="I35" s="2">
         <v>0.0</v>
@@ -1198,33 +1748,45 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>25</v>
+        <v>14</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="I36" s="2">
         <v>0.0</v>
       </c>
       <c r="J36" s="2">
-        <v>2.0</v>
+        <v>-0.5</v>
       </c>
       <c r="K36" s="2">
-        <v>0.0</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>25</v>
+        <v>14</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="I37" s="2">
         <v>0.0</v>
@@ -1238,13 +1800,19 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>25</v>
+        <v>14</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="I38" s="2">
         <v>0.0</v>
@@ -1258,13 +1826,19 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>25</v>
+        <v>14</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="I39" s="2">
         <v>0.0</v>
@@ -1278,13 +1852,19 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>25</v>
+        <v>14</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="I40" s="2">
         <v>0.0</v>
@@ -1298,13 +1878,19 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>25</v>
+        <v>14</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="I41" s="2">
         <v>0.0</v>
@@ -1318,13 +1904,19 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>25</v>
+        <v>14</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="I42" s="2">
         <v>0.0</v>
@@ -1338,13 +1930,19 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>25</v>
+        <v>14</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="I43" s="2">
         <v>0.0</v>
@@ -1358,19 +1956,28 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="H44" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B44" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H44" s="1" t="s">
-        <v>26</v>
-      </c>
       <c r="I44" s="2">
         <v>0.0</v>
       </c>
       <c r="J44" s="2">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="K44" s="2">
         <v>0.0</v>
@@ -1378,13 +1985,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>25</v>
+        <v>63</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="I45" s="2">
         <v>0.0</v>
@@ -1398,13 +2014,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>25</v>
+        <v>63</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="I46" s="2">
         <v>0.0</v>
@@ -1418,13 +2043,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>25</v>
+        <v>63</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="I47" s="2">
         <v>0.0</v>
@@ -1438,13 +2072,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>25</v>
+        <v>63</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="I48" s="2">
         <v>0.0</v>
@@ -1458,13 +2101,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>25</v>
+        <v>63</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="I49" s="2">
         <v>0.0</v>
@@ -1478,13 +2130,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>25</v>
+        <v>63</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="I50" s="2">
         <v>0.0</v>
@@ -1498,13 +2159,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>25</v>
+        <v>63</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="I51" s="2">
         <v>0.0</v>
@@ -1518,13 +2188,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>25</v>
+        <v>63</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="I52" s="2">
         <v>0.0</v>
@@ -1538,13 +2217,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>25</v>
+        <v>63</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="I53" s="2">
         <v>0.0</v>
@@ -1558,13 +2246,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>25</v>
+        <v>63</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="I54" s="2">
         <v>0.0</v>
@@ -1578,13 +2275,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>25</v>
+        <v>63</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="I55" s="2">
         <v>0.0</v>
@@ -1598,13 +2304,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>25</v>
+        <v>63</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="I56" s="2">
         <v>0.0</v>
@@ -1618,13 +2333,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>25</v>
+        <v>63</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="I57" s="2">
         <v>0.0</v>
@@ -1638,13 +2362,19 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B58" s="1">
-        <v>1234.0</v>
+        <v>65</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="I58" s="2">
         <v>0.0</v>
@@ -1658,14 +2388,20 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="H59" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B59" s="1">
-        <v>1234.0</v>
-      </c>
-      <c r="H59" s="1" t="s">
-        <v>27</v>
-      </c>
       <c r="I59" s="2">
         <v>0.0</v>
       </c>
@@ -1673,18 +2409,24 @@
         <v>2.0</v>
       </c>
       <c r="K59" s="2">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B60" s="1">
-        <v>1234.0</v>
+        <v>65</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="I60" s="2">
         <v>0.0</v>
@@ -1698,13 +2440,19 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B61" s="1">
-        <v>1234.0</v>
+        <v>65</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="I61" s="2">
         <v>0.0</v>
@@ -1718,19 +2466,25 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B62" s="1">
-        <v>1234.0</v>
+        <v>65</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="I62" s="2">
         <v>0.0</v>
       </c>
       <c r="J62" s="2">
-        <v>2.0</v>
+        <v>-2.0</v>
       </c>
       <c r="K62" s="2">
         <v>0.0</v>
@@ -1738,33 +2492,45 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B63" s="1">
-        <v>1234.0</v>
+        <v>65</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="I63" s="2">
         <v>0.0</v>
       </c>
       <c r="J63" s="2">
-        <v>2.0</v>
+        <v>-1.5</v>
       </c>
       <c r="K63" s="2">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B64" s="1">
-        <v>1234.0</v>
+        <v>65</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="I64" s="2">
         <v>0.0</v>
@@ -1778,13 +2544,19 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B65" s="1">
-        <v>1234.0</v>
+        <v>65</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="I65" s="2">
         <v>0.0</v>
@@ -1798,13 +2570,19 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B66" s="1">
-        <v>1234.0</v>
+        <v>65</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="I66" s="2">
         <v>0.0</v>
@@ -1818,13 +2596,19 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B67" s="1">
-        <v>1234.0</v>
+        <v>65</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="I67" s="2">
         <v>0.0</v>
@@ -1838,13 +2622,19 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B68" s="1">
-        <v>1234.0</v>
+        <v>65</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="I68" s="2">
         <v>0.0</v>
@@ -1858,13 +2648,19 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B69" s="1">
-        <v>1234.0</v>
+        <v>65</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="I69" s="2">
         <v>0.0</v>
@@ -1878,13 +2674,19 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B70" s="1">
-        <v>1234.0</v>
+        <v>65</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G70" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="I70" s="2">
         <v>0.0</v>
@@ -1898,13 +2700,19 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B71" s="1">
-        <v>1234.0</v>
+        <v>65</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="I71" s="2">
         <v>0.0</v>
@@ -1918,13 +2726,19 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>25</v>
+        <v>69</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="I72" s="2">
         <v>0.0</v>
@@ -1938,13 +2752,19 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>25</v>
+        <v>69</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G73" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="I73" s="2">
         <v>0.0</v>
@@ -1953,18 +2773,24 @@
         <v>2.0</v>
       </c>
       <c r="K73" s="2">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="H74" s="1" t="s">
         <v>44</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H74" s="1" t="s">
-        <v>28</v>
       </c>
       <c r="I74" s="2">
         <v>0.0</v>
@@ -1978,13 +2804,19 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>25</v>
+        <v>69</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G75" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="I75" s="2">
         <v>0.0</v>
@@ -1998,19 +2830,25 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>25</v>
+        <v>69</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G76" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="I76" s="2">
         <v>0.0</v>
       </c>
       <c r="J76" s="2">
-        <v>2.0</v>
+        <v>-2.0</v>
       </c>
       <c r="K76" s="2">
         <v>0.0</v>
@@ -2018,33 +2856,45 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>25</v>
+        <v>69</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="I77" s="2">
         <v>0.0</v>
       </c>
       <c r="J77" s="2">
-        <v>2.0</v>
+        <v>-1.5</v>
       </c>
       <c r="K77" s="2">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>25</v>
+        <v>69</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G78" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="I78" s="2">
         <v>0.0</v>
@@ -2058,13 +2908,19 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>25</v>
+        <v>69</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G79" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="I79" s="2">
         <v>0.0</v>
@@ -2078,13 +2934,19 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>25</v>
+        <v>69</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G80" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="I80" s="2">
         <v>0.0</v>
@@ -2098,13 +2960,19 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>25</v>
+        <v>69</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G81" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="I81" s="2">
         <v>0.0</v>
@@ -2118,13 +2986,19 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>25</v>
+        <v>69</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G82" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="I82" s="2">
         <v>0.0</v>
@@ -2138,13 +3012,19 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>25</v>
+        <v>69</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G83" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="I83" s="2">
         <v>0.0</v>
@@ -2158,13 +3038,19 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>25</v>
+        <v>69</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G84" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="I84" s="2">
         <v>0.0</v>
@@ -2178,13 +3064,19 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>25</v>
+        <v>69</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G85" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="I85" s="2">
         <v>0.0</v>
@@ -2194,6 +3086,185 @@
       </c>
       <c r="K85" s="2">
         <v>0.0</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <sheetData>
+    <row r="1">
+      <c r="C1" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q1" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="R1" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C2" s="2">
+        <v>34.0</v>
+      </c>
+      <c r="D2" s="2">
+        <v>45.0</v>
+      </c>
+      <c r="E2" s="2">
+        <v>225.0</v>
+      </c>
+      <c r="G2" s="2">
+        <v>135.0</v>
+      </c>
+      <c r="I2" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="P2" s="2">
+        <v>22.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C3" s="2">
+        <v>89.0</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="I3" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="P3" s="2">
+        <v>30.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C4" s="2">
+        <v>1415.0</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="I4" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="P4" s="2">
+        <v>20.0</v>
       </c>
     </row>
   </sheetData>
